--- a/dados/peg_quantidade.xlsx
+++ b/dados/peg_quantidade.xlsx
@@ -4073,10 +4073,10 @@
     <t>10072296000452</t>
   </si>
   <si>
-    <t>INSTITUTO ALCIDES DE ANDRADE LIMA</t>
-  </si>
-  <si>
-    <t>HOSPITAL MEMORIAL GUARARAPES</t>
+    <t>INSTITUTO GUARARAPES DE SAUDE</t>
+  </si>
+  <si>
+    <t>HOSPITAL GUARARAPES</t>
   </si>
   <si>
     <t>11490539000192</t>
@@ -16805,13 +16805,13 @@
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B462" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>10</v>
@@ -16823,73 +16823,73 @@
         <v>1219</v>
       </c>
       <c r="G462" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H462" s="2">
-        <v>732</v>
+        <v>239</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="B463" s="0" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>10</v>
       </c>
       <c r="E463" s="0" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="F463" s="0" t="s">
         <v>1219</v>
       </c>
       <c r="G463" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H463" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B464" s="0" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>10</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>1219</v>
       </c>
       <c r="G464" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H464" s="2">
-        <v>149</v>
+        <v>162</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B465" s="0" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>10</v>
@@ -16901,73 +16901,73 @@
         <v>1219</v>
       </c>
       <c r="G465" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H465" s="2">
-        <v>162</v>
+        <v>451</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B466" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>10</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F466" s="0" t="s">
         <v>1219</v>
       </c>
       <c r="G466" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H466" s="2">
-        <v>451</v>
+        <v>250</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B467" s="0" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C467" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D467" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E467" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F467" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G467" s="2">
         <v>27</v>
       </c>
-      <c r="D467" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E467" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F467" s="0" t="s">
-        <v>1219</v>
-      </c>
-      <c r="G467" s="2">
-        <v>28</v>
-      </c>
       <c r="H467" s="2">
-        <v>250</v>
+        <v>168</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
-        <v>49</v>
+        <v>578</v>
       </c>
       <c r="B468" s="0" t="s">
-        <v>50</v>
+        <v>579</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>50</v>
+        <v>580</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>10</v>
@@ -16979,21 +16979,21 @@
         <v>1219</v>
       </c>
       <c r="G468" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H468" s="2">
-        <v>168</v>
+        <v>29</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0" t="s">
-        <v>578</v>
+        <v>46</v>
       </c>
       <c r="B469" s="0" t="s">
-        <v>579</v>
+        <v>47</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>580</v>
+        <v>48</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>10</v>
@@ -17005,21 +17005,21 @@
         <v>1219</v>
       </c>
       <c r="G469" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H469" s="2">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>10</v>
@@ -17031,10 +17031,10 @@
         <v>1219</v>
       </c>
       <c r="G470" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H470" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
     </row>
     <row r="471">
@@ -17091,19 +17091,19 @@
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="B473" s="0" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="D473" s="0" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E473" s="0" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F473" s="0" t="s">
         <v>1219</v>
@@ -17112,24 +17112,24 @@
         <v>13</v>
       </c>
       <c r="H473" s="2">
-        <v>319</v>
+        <v>13</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="0" t="s">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="B474" s="0" t="s">
-        <v>243</v>
+        <v>105</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>10</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>1219</v>
@@ -17138,24 +17138,24 @@
         <v>13</v>
       </c>
       <c r="H474" s="2">
-        <v>35</v>
+        <v>319</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0" t="s">
-        <v>54</v>
+        <v>242</v>
       </c>
       <c r="B475" s="0" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>56</v>
+        <v>243</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F475" s="0" t="s">
         <v>1219</v>
@@ -17164,7 +17164,7 @@
         <v>13</v>
       </c>
       <c r="H475" s="2">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="476">
